--- a/data/colleges.xlsx
+++ b/data/colleges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sepehrakbari/Projects/enrollment-cliff/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7A0846-CB0F-4A49-B55E-0E04C85F94AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C61A2C-9746-9C48-9021-02FA6FAB8227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="288">
   <si>
     <t>index</t>
   </si>
@@ -346,27 +346,18 @@
     <t>Doctoral/Professional Universities</t>
   </si>
   <si>
-    <t>Enrollment; Financial, Pandemic</t>
-  </si>
-  <si>
     <t>Cazenovia College</t>
   </si>
   <si>
     <t>Fringe</t>
   </si>
   <si>
-    <t>Enrollment; Financial; Pandemic</t>
-  </si>
-  <si>
     <t>Chatfield College</t>
   </si>
   <si>
     <t>High Transfer-High Nontraditional</t>
   </si>
   <si>
-    <t>Enrollment; Pandemic; closing to become Chatfield Edge nonprofit agency</t>
-  </si>
-  <si>
     <t>Compass College of Film and Media</t>
   </si>
   <si>
@@ -403,9 +394,6 @@
     <t>Suburb: Large</t>
   </si>
   <si>
-    <t>Financial; Pandemic</t>
-  </si>
-  <si>
     <t>Finlandia University</t>
   </si>
   <si>
@@ -415,9 +403,6 @@
     <t>Evangelical Lutheran</t>
   </si>
   <si>
-    <t>Enrollment; Financial</t>
-  </si>
-  <si>
     <t>Fontbonne University</t>
   </si>
   <si>
@@ -448,9 +433,6 @@
     <t>Holy Family College</t>
   </si>
   <si>
-    <t>Masters Colleges &amp; Universities</t>
-  </si>
-  <si>
     <t>Holy Names University</t>
   </si>
   <si>
@@ -472,9 +454,6 @@
     <t>Other Health Professions Schools</t>
   </si>
   <si>
-    <t>Unclear; sudden closure</t>
-  </si>
-  <si>
     <t>Indiana University-Purdue University Indianapolis</t>
   </si>
   <si>
@@ -487,9 +466,6 @@
     <t>High Research Activity</t>
   </si>
   <si>
-    <t>Mutual Benefit; separating into different institutions</t>
-  </si>
-  <si>
     <t>Iowa Wesleyan University</t>
   </si>
   <si>
@@ -550,9 +526,6 @@
     <t>Mixed Baccalaureate/Associates</t>
   </si>
   <si>
-    <t>Pandemic; Enrollment; Financial</t>
-  </si>
-  <si>
     <t>MacMurray College</t>
   </si>
   <si>
@@ -610,9 +583,6 @@
     <t>Suburb: Small</t>
   </si>
   <si>
-    <t>Enrollment; Financial; Pandemic; failed merger</t>
-  </si>
-  <si>
     <t>Medaille University</t>
   </si>
   <si>
@@ -730,9 +700,6 @@
     <t>University of Nevada (Reno)</t>
   </si>
   <si>
-    <t>Enrollment; Pandemic</t>
-  </si>
-  <si>
     <t>St. Augustine College</t>
   </si>
   <si>
@@ -884,6 +851,39 @@
   </si>
   <si>
     <t>65897;65802</t>
+  </si>
+  <si>
+    <t>Hampshire College</t>
+  </si>
+  <si>
+    <t>Anna Maria College</t>
+  </si>
+  <si>
+    <t>Enrollment, Financial, Pandemic</t>
+  </si>
+  <si>
+    <t>Enrollment, Pandemic, closing to become Chatfield Edge nonprofit agency</t>
+  </si>
+  <si>
+    <t>Financial, Pandemic</t>
+  </si>
+  <si>
+    <t>Enrollment, Financial</t>
+  </si>
+  <si>
+    <t>Unclear, sudden closure</t>
+  </si>
+  <si>
+    <t>Mutual Benefit, separating into different institutions</t>
+  </si>
+  <si>
+    <t>Pandemic, Enrollment, Financial</t>
+  </si>
+  <si>
+    <t>Enrollment, Financial, Pandemic, failed merger</t>
+  </si>
+  <si>
+    <t>Enrollment, Pandemic</t>
   </si>
 </sst>
 </file>
@@ -972,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -985,6 +985,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1287,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO68"/>
+  <dimension ref="A1:AO70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -2484,7 +2486,7 @@
         <v>0</v>
       </c>
       <c r="AH10" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="AI10" s="5">
         <v>12087176</v>
@@ -2516,7 +2518,7 @@
         <v>189848</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D11">
         <v>1824</v>
@@ -2534,7 +2536,7 @@
         <v>94</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J11" t="s">
         <v>46</v>
@@ -2603,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="AH11" t="s">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="AI11" s="5">
         <v>7668092</v>
@@ -2635,7 +2637,7 @@
         <v>201751</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>1971</v>
@@ -2683,7 +2685,7 @@
         <v>73</v>
       </c>
       <c r="U12" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="V12">
         <v>2023</v>
@@ -2722,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="AH12" t="s">
-        <v>114</v>
+        <v>280</v>
       </c>
       <c r="AI12" s="5">
         <v>4771003</v>
@@ -2754,16 +2756,16 @@
         <v>459417</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>1997</v>
       </c>
       <c r="E13" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G13">
         <v>49503</v>
@@ -2799,10 +2801,10 @@
         <v>50</v>
       </c>
       <c r="T13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="V13">
         <v>2023</v>
@@ -2811,7 +2813,7 @@
         <v>75</v>
       </c>
       <c r="X13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Y13">
         <v>3231</v>
@@ -2823,10 +2825,10 @@
         <v>49546</v>
       </c>
       <c r="AB13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AC13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2859,7 +2861,7 @@
         <v>190248</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D14">
         <v>1881</v>
@@ -2895,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -2916,7 +2918,7 @@
         <v>75</v>
       </c>
       <c r="X14" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="Y14">
         <v>3621</v>
@@ -2928,7 +2930,7 @@
         <v>10801</v>
       </c>
       <c r="AB14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC14" t="s">
         <v>79</v>
@@ -2946,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="AH14" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="AI14" s="5">
         <v>12661592</v>
@@ -2978,16 +2980,16 @@
         <v>172440</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D15">
         <v>1896</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G15">
         <v>49930</v>
@@ -2996,7 +2998,7 @@
         <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J15" t="s">
         <v>46</v>
@@ -3014,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -3065,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="AH15" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI15" s="5">
         <v>7958061</v>
@@ -3097,16 +3099,16 @@
         <v>177418</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D16">
         <v>1923</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F16" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G16">
         <v>63105</v>
@@ -3184,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="AH16" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI16" s="5">
         <v>14669491</v>
@@ -3216,16 +3218,16 @@
         <v>367884</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <v>1990</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G17">
         <v>33966</v>
@@ -3234,7 +3236,7 @@
         <v>58</v>
       </c>
       <c r="I17" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J17" t="s">
         <v>46</v>
@@ -3258,13 +3260,13 @@
         <v>1</v>
       </c>
       <c r="S17" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="T17" t="s">
         <v>61</v>
       </c>
       <c r="U17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V17">
         <v>2024</v>
@@ -3335,7 +3337,7 @@
         <v>239743</v>
       </c>
       <c r="C18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D18">
         <v>1935</v>
@@ -3380,10 +3382,10 @@
         <v>50</v>
       </c>
       <c r="T18" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="U18" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V18">
         <v>2020</v>
@@ -3422,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="s">
-        <v>111</v>
+        <v>279</v>
       </c>
       <c r="AI18" s="5">
         <v>7048441</v>
@@ -3454,16 +3456,16 @@
         <v>115728</v>
       </c>
       <c r="C19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D19">
         <v>1868</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G19">
         <v>94619</v>
@@ -3502,7 +3504,7 @@
         <v>61</v>
       </c>
       <c r="U19" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V19">
         <v>2023</v>
@@ -3541,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="AH19" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI19" s="5">
         <v>51917540</v>
@@ -3573,16 +3575,16 @@
         <v>465812</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D20">
         <v>1978</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F20" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G20">
         <v>84401</v>
@@ -3618,10 +3620,10 @@
         <v>50</v>
       </c>
       <c r="T20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U20" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V20">
         <v>2021</v>
@@ -3660,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="AH20" t="s">
-        <v>150</v>
+        <v>283</v>
       </c>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
@@ -3678,7 +3680,7 @@
         <v>151111</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D21">
         <v>1969</v>
@@ -3699,7 +3701,7 @@
         <v>59</v>
       </c>
       <c r="J21" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K21" t="s">
         <v>47</v>
@@ -3723,10 +3725,10 @@
         <v>50</v>
       </c>
       <c r="T21" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="U21" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="V21">
         <v>2024</v>
@@ -3765,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="AH21" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="AI21" s="5">
         <v>1177983781</v>
@@ -3797,16 +3799,16 @@
         <v>153621</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D22">
         <v>1842</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="G22">
         <v>52641</v>
@@ -3815,7 +3817,7 @@
         <v>94</v>
       </c>
       <c r="I22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J22" t="s">
         <v>46</v>
@@ -3833,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3916,16 +3918,16 @@
         <v>132879</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="D23">
         <v>1893</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G23">
         <v>34744</v>
@@ -3952,7 +3954,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3961,10 +3963,10 @@
         <v>50</v>
       </c>
       <c r="T23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U23" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="V23">
         <v>2024</v>
@@ -4003,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="AH23" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI23" s="5">
         <v>1425097</v>
@@ -4035,16 +4037,16 @@
         <v>101541</v>
       </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="D24">
         <v>1838</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F24" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G24">
         <v>36756</v>
@@ -4154,16 +4156,16 @@
         <v>146667</v>
       </c>
       <c r="C25" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D25">
         <v>1944</v>
       </c>
       <c r="E25" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F25" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G25">
         <v>62656</v>
@@ -4190,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -4202,7 +4204,7 @@
         <v>61</v>
       </c>
       <c r="U25" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V25">
         <v>2024</v>
@@ -4211,7 +4213,7 @@
         <v>75</v>
       </c>
       <c r="X25" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="Y25">
         <v>689</v>
@@ -4223,10 +4225,10 @@
         <v>64801</v>
       </c>
       <c r="AB25" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC25" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="AD25">
         <v>1</v>
@@ -4241,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI25" s="5">
         <v>5336831</v>
@@ -4273,16 +4275,16 @@
         <v>146676</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="D26">
         <v>1865</v>
       </c>
       <c r="E26" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F26" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G26">
         <v>62656</v>
@@ -4315,13 +4317,13 @@
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="T26" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="U26" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="V26">
         <v>2022</v>
@@ -4360,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="s">
-        <v>176</v>
+        <v>285</v>
       </c>
       <c r="AI26" s="5">
         <v>1969345</v>
@@ -4392,16 +4394,16 @@
         <v>146825</v>
       </c>
       <c r="C27" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D27">
         <v>1846</v>
       </c>
       <c r="E27" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G27">
         <v>62650</v>
@@ -4410,7 +4412,7 @@
         <v>44</v>
       </c>
       <c r="I27" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J27" t="s">
         <v>46</v>
@@ -4428,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -4511,16 +4513,16 @@
         <v>182917</v>
       </c>
       <c r="C28" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D28">
         <v>1973</v>
       </c>
       <c r="E28" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F28" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G28">
         <v>3278</v>
@@ -4598,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
@@ -4616,16 +4618,16 @@
         <v>230940</v>
       </c>
       <c r="C29" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D29">
         <v>1946</v>
       </c>
       <c r="E29" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F29" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G29">
         <v>5344</v>
@@ -4673,7 +4675,7 @@
         <v>75</v>
       </c>
       <c r="X29" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="Y29">
         <v>5891</v>
@@ -4703,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="AH29" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI29" s="5">
         <v>37619624</v>
@@ -4735,16 +4737,16 @@
         <v>220701</v>
       </c>
       <c r="C30" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D30">
         <v>1870</v>
       </c>
       <c r="E30" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F30" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="G30">
         <v>38478</v>
@@ -4792,19 +4794,19 @@
         <v>75</v>
       </c>
       <c r="X30" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="Y30">
         <v>49000</v>
       </c>
       <c r="Z30" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AA30">
         <v>37996</v>
       </c>
       <c r="AB30" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="AC30" t="s">
         <v>50</v>
@@ -4840,16 +4842,16 @@
         <v>118541</v>
       </c>
       <c r="C31" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D31">
         <v>1932</v>
       </c>
       <c r="E31" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F31" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G31">
         <v>90275</v>
@@ -4894,10 +4896,10 @@
         <v>2022</v>
       </c>
       <c r="W31" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="X31" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="Y31">
         <v>10242</v>
@@ -4909,7 +4911,7 @@
         <v>33574</v>
       </c>
       <c r="AB31" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AC31" t="s">
         <v>72</v>
@@ -4927,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="AI31" s="5">
         <v>12360679</v>
@@ -4959,7 +4961,7 @@
         <v>192925</v>
       </c>
       <c r="C32" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D32">
         <v>1937</v>
@@ -5046,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="AH32" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI32" s="5">
         <v>1470738</v>
@@ -5078,16 +5080,16 @@
         <v>118888</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D33">
         <v>1852</v>
       </c>
       <c r="E33" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F33" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G33">
         <v>94613</v>
@@ -5123,7 +5125,7 @@
         <v>50</v>
       </c>
       <c r="T33" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="U33" t="s">
         <v>62</v>
@@ -5135,7 +5137,7 @@
         <v>75</v>
       </c>
       <c r="X33" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="Y33">
         <v>30013</v>
@@ -5165,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="AH33" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AI33" s="5">
         <v>191278617</v>
@@ -5197,16 +5199,16 @@
         <v>209287</v>
       </c>
       <c r="C34" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D34">
         <v>1936</v>
       </c>
       <c r="E34" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F34" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G34">
         <v>97220</v>
@@ -5242,7 +5244,7 @@
         <v>50</v>
       </c>
       <c r="T34" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="U34" t="s">
         <v>52</v>
@@ -5254,7 +5256,7 @@
         <v>75</v>
       </c>
       <c r="X34" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="Y34">
         <v>1624</v>
@@ -5266,7 +5268,7 @@
         <v>95765</v>
       </c>
       <c r="AB34" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="AC34" t="s">
         <v>60</v>
@@ -5313,16 +5315,16 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D35">
         <v>1945</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="F35" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="G35">
         <v>68046</v>
@@ -5349,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -5358,10 +5360,10 @@
         <v>50</v>
       </c>
       <c r="T35" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U35" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="V35">
         <v>2020</v>
@@ -5400,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="AH35" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
@@ -5418,7 +5420,7 @@
         <v>204468</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D36">
         <v>1922</v>
@@ -5537,7 +5539,7 @@
         <v>237640</v>
       </c>
       <c r="C37" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D37">
         <v>1960</v>
@@ -5555,7 +5557,7 @@
         <v>58</v>
       </c>
       <c r="I37" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J37" t="s">
         <v>46</v>
@@ -5573,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -5656,16 +5658,16 @@
         <v>209603</v>
       </c>
       <c r="C38" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D38">
         <v>1909</v>
       </c>
       <c r="E38" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F38" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="G38">
         <v>97209</v>
@@ -5701,10 +5703,10 @@
         <v>50</v>
       </c>
       <c r="T38" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U38" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="V38">
         <v>2021</v>
@@ -5713,7 +5715,7 @@
         <v>75</v>
       </c>
       <c r="X38" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="Y38">
         <v>1909</v>
@@ -5725,7 +5727,7 @@
         <v>97301</v>
       </c>
       <c r="AB38" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AC38" t="s">
         <v>50</v>
@@ -5761,7 +5763,7 @@
         <v>442356</v>
       </c>
       <c r="C39" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D39">
         <v>1903</v>
@@ -5806,10 +5808,10 @@
         <v>50</v>
       </c>
       <c r="T39" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U39" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V39">
         <v>2024</v>
@@ -5818,7 +5820,7 @@
         <v>75</v>
       </c>
       <c r="X39" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="Y39">
         <v>7861</v>
@@ -5833,7 +5835,7 @@
         <v>78</v>
       </c>
       <c r="AC39" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="AD39">
         <v>0</v>
@@ -5880,7 +5882,7 @@
         <v>167455</v>
       </c>
       <c r="C40" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="D40">
         <v>1911</v>
@@ -5937,7 +5939,7 @@
         <v>75</v>
       </c>
       <c r="X40" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="Y40">
         <v>15287</v>
@@ -5949,7 +5951,7 @@
         <v>2467</v>
       </c>
       <c r="AB40" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC40" t="s">
         <v>50</v>
@@ -5999,16 +6001,16 @@
         <v>219295</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D41">
         <v>1951</v>
       </c>
       <c r="E41" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F41" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G41">
         <v>57401</v>
@@ -6017,7 +6019,7 @@
         <v>94</v>
       </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J41" t="s">
         <v>46</v>
@@ -6044,10 +6046,10 @@
         <v>50</v>
       </c>
       <c r="T41" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U41" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V41">
         <v>2023</v>
@@ -6118,16 +6120,16 @@
         <v>486433</v>
       </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D42">
         <v>2003</v>
       </c>
       <c r="E42" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G42">
         <v>94129</v>
@@ -6145,7 +6147,7 @@
         <v>47</v>
       </c>
       <c r="L42" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="O42">
         <v>197</v>
@@ -6160,13 +6162,13 @@
         <v>1</v>
       </c>
       <c r="S42" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="T42" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U42" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="V42">
         <v>2023</v>
@@ -6175,7 +6177,7 @@
         <v>75</v>
       </c>
       <c r="X42" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="Y42">
         <v>3460</v>
@@ -6187,10 +6189,10 @@
         <v>92373</v>
       </c>
       <c r="AB42" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC42" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AD42">
         <v>1</v>
@@ -6223,7 +6225,7 @@
         <v>214564</v>
       </c>
       <c r="C43" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D43">
         <v>1919</v>
@@ -6250,7 +6252,7 @@
         <v>47</v>
       </c>
       <c r="L43" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="O43">
         <v>1165</v>
@@ -6268,10 +6270,10 @@
         <v>50</v>
       </c>
       <c r="T43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U43" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V43">
         <v>2024</v>
@@ -6280,7 +6282,7 @@
         <v>75</v>
       </c>
       <c r="X43" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="Y43">
         <v>22344</v>
@@ -6342,16 +6344,16 @@
         <v>122454</v>
       </c>
       <c r="C44" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D44">
         <v>1871</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F44" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G44">
         <v>94133</v>
@@ -6387,10 +6389,10 @@
         <v>50</v>
       </c>
       <c r="T44" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U44" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="V44">
         <v>2022</v>
@@ -6461,16 +6463,16 @@
         <v>182458</v>
       </c>
       <c r="C45" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D45">
         <v>1969</v>
       </c>
       <c r="E45" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="F45" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="G45">
         <v>89451</v>
@@ -6518,13 +6520,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="Y45">
         <v>20945</v>
       </c>
       <c r="Z45" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AA45">
         <v>89557</v>
@@ -6548,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="AI45" s="5">
         <v>4382400</v>
@@ -6580,16 +6582,16 @@
         <v>148876</v>
       </c>
       <c r="C46" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D46">
         <v>1980</v>
       </c>
       <c r="E46" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F46" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G46">
         <v>60640</v>
@@ -6616,19 +6618,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
       <c r="S46" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="T46" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="U46" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="V46">
         <v>2024</v>
@@ -6637,7 +6639,7 @@
         <v>75</v>
       </c>
       <c r="X46" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="Y46">
         <v>6513</v>
@@ -6649,10 +6651,10 @@
         <v>60446</v>
       </c>
       <c r="AB46" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AC46" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6699,7 +6701,7 @@
         <v>19580901</v>
       </c>
       <c r="C47" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="D47">
         <v>1933</v>
@@ -6744,7 +6746,7 @@
         <v>50</v>
       </c>
       <c r="T47" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U47" t="s">
         <v>52</v>
@@ -6786,7 +6788,7 @@
         <v>0</v>
       </c>
       <c r="AH47" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
@@ -6804,16 +6806,16 @@
         <v>179256</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D48">
         <v>1956</v>
       </c>
       <c r="E48" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F48" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G48">
         <v>63033</v>
@@ -6840,7 +6842,7 @@
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -6849,10 +6851,10 @@
         <v>50</v>
       </c>
       <c r="T48" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U48" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="V48">
         <v>2022</v>
@@ -6861,7 +6863,7 @@
         <v>75</v>
       </c>
       <c r="X48" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="Y48">
         <v>190</v>
@@ -6891,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI48" s="5">
         <v>1120476</v>
@@ -6923,7 +6925,7 @@
         <v>195234</v>
       </c>
       <c r="C49" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="D49">
         <v>1920</v>
@@ -6941,7 +6943,7 @@
         <v>58</v>
       </c>
       <c r="I49" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J49" t="s">
         <v>46</v>
@@ -7042,7 +7044,7 @@
         <v>215132</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D50">
         <v>1821</v>
@@ -7087,10 +7089,10 @@
         <v>50</v>
       </c>
       <c r="T50" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U50" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V50">
         <v>2022</v>
@@ -7099,7 +7101,7 @@
         <v>75</v>
       </c>
       <c r="X50" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="Y50">
         <v>7861</v>
@@ -7158,7 +7160,7 @@
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D51">
         <v>1850</v>
@@ -7245,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="AH51" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
@@ -7263,7 +7265,7 @@
         <v>240365</v>
       </c>
       <c r="C52" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="D52">
         <v>1968</v>
@@ -7281,10 +7283,10 @@
         <v>58</v>
       </c>
       <c r="I52" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J52" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K52" t="s">
         <v>47</v>
@@ -7350,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="AH52" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
@@ -7368,7 +7370,7 @@
         <v>240277</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D53">
         <v>1935</v>
@@ -7389,7 +7391,7 @@
         <v>67</v>
       </c>
       <c r="J53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K53" t="s">
         <v>47</v>
@@ -7455,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="AH53" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
@@ -7473,7 +7475,7 @@
         <v>240453</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="D54">
         <v>1966</v>
@@ -7494,7 +7496,7 @@
         <v>59</v>
       </c>
       <c r="J54" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K54" t="s">
         <v>47</v>
@@ -7518,10 +7520,10 @@
         <v>50</v>
       </c>
       <c r="T54" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="U54" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="V54">
         <v>2025</v>
@@ -7560,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="AH54" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
@@ -7578,7 +7580,7 @@
         <v>240453</v>
       </c>
       <c r="C55" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="D55">
         <v>1968</v>
@@ -7599,7 +7601,7 @@
         <v>59</v>
       </c>
       <c r="J55" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K55" t="s">
         <v>47</v>
@@ -7623,10 +7625,10 @@
         <v>50</v>
       </c>
       <c r="T55" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="U55" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="V55">
         <v>2024</v>
@@ -7665,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="AH55" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
@@ -7680,16 +7682,16 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="D56">
         <v>1999</v>
       </c>
       <c r="E56" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="F56" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="G56">
         <v>23454</v>
@@ -7767,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="AH56" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
@@ -7785,16 +7787,16 @@
         <v>131098</v>
       </c>
       <c r="C57" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D57">
         <v>1873</v>
       </c>
       <c r="E57" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="F57" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="G57">
         <v>19901</v>
@@ -7821,7 +7823,7 @@
         <v>1</v>
       </c>
       <c r="Q57" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -7842,19 +7844,19 @@
         <v>75</v>
       </c>
       <c r="X57" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="Y57">
         <v>5826</v>
       </c>
       <c r="Z57" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AA57">
         <v>19901</v>
       </c>
       <c r="AB57" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC57" t="s">
         <v>50</v>
@@ -7872,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="AH57" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI57" s="5">
         <v>3281329</v>
@@ -7904,16 +7906,16 @@
         <v>125897</v>
       </c>
       <c r="C58" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="D58">
         <v>1884</v>
       </c>
       <c r="E58" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F58" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G58">
         <v>91504</v>
@@ -7952,7 +7954,7 @@
         <v>61</v>
       </c>
       <c r="U58" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V58">
         <v>2024</v>
@@ -7961,7 +7963,7 @@
         <v>75</v>
       </c>
       <c r="X58" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="Y58">
         <v>3460</v>
@@ -7973,10 +7975,10 @@
         <v>92373</v>
       </c>
       <c r="AB58" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC58" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="AD58">
         <v>1</v>
@@ -7991,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="AH58" t="s">
-        <v>131</v>
+        <v>282</v>
       </c>
       <c r="AI58" s="5">
         <v>22197101</v>
@@ -8023,16 +8025,16 @@
         <v>149763</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D59">
         <v>1914</v>
       </c>
       <c r="E59" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F59" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G59">
         <v>60523</v>
@@ -8074,10 +8076,10 @@
         <v>50</v>
       </c>
       <c r="T59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U59" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V59">
         <v>2024</v>
@@ -8116,7 +8118,7 @@
         <v>0</v>
       </c>
       <c r="AH59" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
@@ -8134,16 +8136,16 @@
         <v>100937</v>
       </c>
       <c r="C60" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D60">
         <v>1918</v>
       </c>
       <c r="E60" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F60" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G60">
         <v>35254</v>
@@ -8170,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="Q60" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -8253,16 +8255,16 @@
         <v>207935</v>
       </c>
       <c r="C61" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D61">
         <v>1970</v>
       </c>
       <c r="E61" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="F61" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="G61">
         <v>74055</v>
@@ -8274,7 +8276,7 @@
         <v>59</v>
       </c>
       <c r="J61" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K61" t="s">
         <v>47</v>
@@ -8310,19 +8312,19 @@
         <v>75</v>
       </c>
       <c r="X61" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="Y61">
         <v>15568</v>
       </c>
       <c r="Z61" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AA61">
         <v>74119</v>
       </c>
       <c r="AB61" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s">
         <v>50</v>
@@ -8340,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="AH61" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AI61" s="5">
         <v>1130654</v>
@@ -8372,7 +8374,7 @@
         <v>197230</v>
       </c>
       <c r="C62" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D62">
         <v>1868</v>
@@ -8491,7 +8493,7 @@
         <v>165644</v>
       </c>
       <c r="C63" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="D63">
         <v>1900</v>
@@ -8527,7 +8529,7 @@
         <v>1</v>
       </c>
       <c r="Q63" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -8539,7 +8541,7 @@
         <v>61</v>
       </c>
       <c r="U63" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="V63">
         <v>2024</v>
@@ -8610,16 +8612,16 @@
         <v>176770</v>
       </c>
       <c r="C64" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="D64">
         <v>1907</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G64">
         <v>65802</v>
@@ -8661,10 +8663,10 @@
         <v>50</v>
       </c>
       <c r="T64" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U64" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V64">
         <v>2025</v>
@@ -8673,19 +8675,19 @@
         <v>75</v>
       </c>
       <c r="X64" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="Y64" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="Z64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AA64" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="AB64" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="AC64" t="s">
         <v>50</v>
@@ -8715,7 +8717,7 @@
         <v>240462</v>
       </c>
       <c r="C65" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D65">
         <v>1967</v>
@@ -8736,7 +8738,7 @@
         <v>45</v>
       </c>
       <c r="J65" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K65" t="s">
         <v>47</v>
@@ -8808,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="AH65" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AO65" s="5"/>
     </row>
@@ -8820,16 +8822,16 @@
         <v>164085</v>
       </c>
       <c r="C66" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D66">
         <v>1974</v>
       </c>
       <c r="E66" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F66" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="G66">
         <v>20723</v>
@@ -8847,7 +8849,7 @@
         <v>47</v>
       </c>
       <c r="L66" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -8871,10 +8873,10 @@
         <v>50</v>
       </c>
       <c r="T66" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="U66" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="V66">
         <v>2025</v>
@@ -8883,7 +8885,7 @@
         <v>75</v>
       </c>
       <c r="X66" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="Y66">
         <v>1836</v>
@@ -8922,16 +8924,16 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="D67">
         <v>2004</v>
       </c>
       <c r="E67" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="F67" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="G67">
         <v>76010</v>
@@ -8949,7 +8951,7 @@
         <v>47</v>
       </c>
       <c r="L67" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -8973,7 +8975,7 @@
         <v>107</v>
       </c>
       <c r="U67" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="V67">
         <v>2025</v>
@@ -8982,7 +8984,7 @@
         <v>75</v>
       </c>
       <c r="X67" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="Y67">
         <v>1833</v>
@@ -9016,8 +9018,259 @@
       </c>
       <c r="AO67" s="5"/>
     </row>
-    <row r="68" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="1:41" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>66</v>
+      </c>
+      <c r="B68" s="8">
+        <v>166018</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="D68" s="8">
+        <v>1965</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G68" s="8">
+        <v>1002</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="J68" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K68" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M68" s="8">
+        <v>1</v>
+      </c>
+      <c r="N68" s="8">
+        <v>0</v>
+      </c>
+      <c r="O68" s="8">
+        <v>844</v>
+      </c>
+      <c r="P68" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R68" s="8">
+        <v>0</v>
+      </c>
+      <c r="S68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="T68" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="U68" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="V68" s="8">
+        <v>2026</v>
+      </c>
+      <c r="W68" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="X68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC68" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD68" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AI68" s="8">
+        <v>58400000</v>
+      </c>
+      <c r="AJ68" s="8">
+        <v>57100000</v>
+      </c>
+      <c r="AK68" s="8">
+        <v>54600000</v>
+      </c>
+      <c r="AL68" s="8">
+        <v>55600000</v>
+      </c>
+      <c r="AM68" s="8">
+        <v>39700000</v>
+      </c>
+      <c r="AN68" s="8">
+        <v>32000000</v>
+      </c>
+      <c r="AO68" s="8">
+        <v>26500000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8">
+        <v>164492</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D69" s="8">
+        <v>1946</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G69" s="9">
+        <v>1612</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="J69" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K69" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L69" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M69" s="8">
+        <v>1</v>
+      </c>
+      <c r="N69" s="8">
+        <v>1</v>
+      </c>
+      <c r="O69" s="8">
+        <v>1202</v>
+      </c>
+      <c r="P69" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q69" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="R69" s="8">
+        <v>0</v>
+      </c>
+      <c r="S69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="T69" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="U69" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="V69" s="8">
+        <v>2026</v>
+      </c>
+      <c r="W69" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="X69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD69" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE69" s="8">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="8">
+        <v>1</v>
+      </c>
+      <c r="AG69" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI69" s="8">
+        <v>5150000</v>
+      </c>
+      <c r="AJ69" s="8">
+        <v>5560000</v>
+      </c>
+      <c r="AK69" s="8">
+        <v>6020000</v>
+      </c>
+      <c r="AL69" s="8">
+        <v>7190000</v>
+      </c>
+      <c r="AM69" s="8">
+        <v>5820000</v>
+      </c>
+      <c r="AN69" s="8">
+        <v>1410000</v>
+      </c>
+      <c r="AO69" s="8">
+        <v>1520000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>